--- a/data/trans_camb/P1427-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P1427-Provincia-trans_camb.xlsx
@@ -598,7 +598,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>-3,09</t>
+          <t>-2,95</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>-2,67</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>-1,43</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
           <t>-2,81</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,43</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-2,96</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,8; -0,13</t>
+          <t>-4,8; -0,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,72; -1,35</t>
+          <t>-5,61; -1,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,73</t>
+          <t>-3,81; 2,83</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -0,88</t>
+          <t>-5,69; -0,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 0,61</t>
+          <t>-3,46; 0,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,99; -1,54</t>
+          <t>-4,74; -1,27</t>
         </is>
       </c>
     </row>
@@ -674,7 +674,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>-91,23%</t>
+          <t>-87,0%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-74,74%</t>
+          <t>-70,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-82,88%</t>
+          <t>-78,6%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-94,19; 11,9</t>
+          <t>-93,69; 10,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -38,64</t>
+          <t>-100,0; -41,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-73,08; 133,19</t>
+          <t>-70,54; 155,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-92,15; -24,52</t>
+          <t>-90,82; -19,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-74,01; 29,38</t>
+          <t>-74,21; 28,44</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-93,46; -58,61</t>
+          <t>-91,1; -50,83</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,31</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,22</t>
+          <t>1,29</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,03</t>
+          <t>-1,88; 0,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 2,87</t>
+          <t>-0,25; 2,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,02</t>
+          <t>-3,38; 0,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,05</t>
+          <t>-0,64; 3,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,33; -0,3</t>
+          <t>-2,3; -0,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 2,44</t>
+          <t>-0,09; 2,49</t>
         </is>
       </c>
     </row>
@@ -830,7 +830,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>113,23%</t>
+          <t>116,69%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>69,62%</t>
         </is>
       </c>
     </row>
@@ -868,27 +868,27 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-28,97; 695,76</t>
+          <t>-30,67; 637,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-86,23; 22,41</t>
+          <t>-86,21; 21,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-31,53; 181,12</t>
+          <t>-19,05; 212,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-87,73; -3,72</t>
+          <t>-86,29; -4,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,35; 206,35</t>
+          <t>-10,21; 201,75</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,52</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,01</t>
+          <t>3,93</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,26</t>
+          <t>4,16</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,9</t>
+          <t>-1,81; 1,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,02</t>
+          <t>2,12; 7,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,84</t>
+          <t>-2,24; 1,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,99</t>
+          <t>1,43; 6,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,38</t>
+          <t>-1,49; 1,24</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,52; 5,95</t>
+          <t>2,56; 5,86</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>298,66%</t>
+          <t>291,41%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>214,78%</t>
+          <t>210,43%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>251,19%</t>
+          <t>245,55%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-78,77; 347,19</t>
+          <t>-79,53; 385,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>60,15; 1063,62</t>
+          <t>51,64; 1081,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-82,93; 289,9</t>
+          <t>-80,42; 283,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>35,61; 768,58</t>
+          <t>32,59; 708,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-59,92; 148,5</t>
+          <t>-62,43; 128,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>81,39; 586,05</t>
+          <t>90,59; 556,95</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>-0,13</t>
+          <t>-0,41</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,53</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-0,8</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; -0,1</t>
+          <t>-3,52; 0,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 1,91</t>
+          <t>-2,45; 1,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,5</t>
+          <t>-3,96; 0,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,85; 0,41</t>
+          <t>-3,42; 0,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,2; -0,08</t>
+          <t>-2,99; -0,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 0,53</t>
+          <t>-2,38; 0,55</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>-5,88%</t>
+          <t>-17,89%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-45,26%</t>
+          <t>-35,05%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-30,75%</t>
+          <t>-28,07%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,51</t>
+          <t>-93,06; 30,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-68,23; 190,62</t>
+          <t>-69,08; 141,74</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-86,72; 38,91</t>
+          <t>-84,09; 51,86</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-74,52; 22,55</t>
+          <t>-68,36; 35,01</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-82,38; 1,5</t>
+          <t>-80,82; 10,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-63,93; 27,45</t>
+          <t>-59,5; 30,41</t>
         </is>
       </c>
     </row>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-1,9</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-0,87</t>
+          <t>-1,14</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,89; -2,14</t>
+          <t>-8,95; -2,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 3,37</t>
+          <t>-4,17; 3,04</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 1,53</t>
+          <t>-6,66; 1,51</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 1,43</t>
+          <t>-6,1; 0,96</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -1,34</t>
+          <t>-5,93; -1,28</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 1,51</t>
+          <t>-3,93; 1,18</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>-7,31%</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-31,61%</t>
+          <t>-34,9%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-17,29%</t>
+          <t>-22,77%</t>
         </is>
       </c>
     </row>
@@ -1336,27 +1336,27 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-58,15; 131,89</t>
+          <t>-59,01; 135,82</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-80,75; 70,99</t>
+          <t>-82,2; 68,52</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-70,66; 55,99</t>
+          <t>-69,59; 37,91</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-89,86; -28,29</t>
+          <t>-90,01; -21,42</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-51,32; 48,16</t>
+          <t>-55,01; 40,03</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>10,0</t>
+          <t>9,9</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>10,69</t>
+          <t>10,56</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>10,33</t>
+          <t>10,22</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 2,75</t>
+          <t>-0,86; 2,55</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7,16; 13,25</t>
+          <t>7,31; 13,32</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 4,29</t>
+          <t>-0,56; 4,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7,78; 13,61</t>
+          <t>7,71; 13,39</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 3,06</t>
+          <t>-0,2; 3,03</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,38; 12,39</t>
+          <t>8,24; 12,25</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1278,33%</t>
+          <t>1265,06%</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>749,91%</t>
+          <t>740,85%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>933,33%</t>
+          <t>923,47%</t>
         </is>
       </c>
     </row>
@@ -1492,27 +1492,27 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>239,03; —</t>
+          <t>271,9; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-47,38; 853,25</t>
+          <t>-45,67; 728,62</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>235,8; 3292,22</t>
+          <t>285,62; 3154,69</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 532,26</t>
+          <t>-21,79; 639,28</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>386,48; 2487,36</t>
+          <t>397,13; 2710,14</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,0</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>4,19</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,08</t>
+          <t>2,65</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,02</t>
+          <t>-2,16; 1,11</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 3,01</t>
+          <t>-0,79; 3,0</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,29</t>
+          <t>-1,25; 2,6</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 5,26</t>
+          <t>2,33; 6,24</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,38</t>
+          <t>-0,99; 1,44</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,52</t>
+          <t>1,33; 4,03</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>123,41%</t>
+          <t>188,07%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>120,9%</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-68,5; 84,93</t>
+          <t>-65,93; 89,87</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 235,29</t>
+          <t>-29,41; 218,68</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-42,27; 153,54</t>
+          <t>-42,79; 188,86</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 316,17</t>
+          <t>68,34; 458,74</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-39,01; 86,87</t>
+          <t>-35,68; 94,48</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>18,05; 217,08</t>
+          <t>42,19; 260,95</t>
         </is>
       </c>
     </row>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>-0,67</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1,01</t>
+          <t>0,27</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,02</t>
+          <t>-0,05</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,5</t>
+          <t>-2,06; 0,47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,47</t>
+          <t>-1,76; 0,64</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 1,61</t>
+          <t>-1,37; 1,71</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,49</t>
+          <t>-1,31; 1,56</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,65</t>
+          <t>-1,28; 0,65</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,35</t>
+          <t>-1,03; 0,87</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>-39,3%</t>
+          <t>-22,09%</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>-2,38%</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-79,85; 72,41</t>
+          <t>-81,68; 58,74</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-81,33; 58,48</t>
+          <t>-67,08; 67,89</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-52,64; 114,77</t>
+          <t>-48,43; 117,19</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-29,09; 229,9</t>
+          <t>-37,84; 108,05</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-51,63; 46,63</t>
+          <t>-52,67; 44,0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-46,25; 82,11</t>
+          <t>-40,25; 60,93</t>
         </is>
       </c>
     </row>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>1,07</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -1856,7 +1856,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1,64</t>
+          <t>1,79</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,47</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-1,59; -0,35</t>
+          <t>-1,58; -0,33</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,83</t>
+          <t>0,35; 1,85</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,37</t>
+          <t>-1,09; 0,38</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,45</t>
+          <t>1,06; 2,5</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,17; -0,14</t>
+          <t>-1,09; -0,14</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,92</t>
+          <t>0,9; 1,96</t>
         </is>
       </c>
     </row>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>63,27%</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-65,59; -20,24</t>
+          <t>-65,58; -19,53</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>5,28; 111,94</t>
+          <t>14,11; 116,96</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 15,16</t>
+          <t>-36,48; 18,73</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>16,11; 109,35</t>
+          <t>33,82; 114,84</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-45,07; -6,62</t>
+          <t>-42,86; -6,16</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>25,34; 93,02</t>
+          <t>35,26; 96,14</t>
         </is>
       </c>
     </row>
